--- a/artfynd/A 55334-2024 artfynd.xlsx
+++ b/artfynd/A 55334-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128692035</v>
       </c>
       <c r="B2" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128691766</v>
       </c>
       <c r="B3" t="n">
-        <v>86888</v>
+        <v>86890</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>128691679</v>
       </c>
       <c r="B4" t="n">
-        <v>90232</v>
+        <v>90234</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 55334-2024 artfynd.xlsx
+++ b/artfynd/A 55334-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128692035</v>
       </c>
       <c r="B2" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55334-2024 artfynd.xlsx
+++ b/artfynd/A 55334-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128692035</v>
       </c>
       <c r="B2" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128691766</v>
       </c>
       <c r="B3" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>128691679</v>
       </c>
       <c r="B4" t="n">
-        <v>90234</v>
+        <v>90261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 55334-2024 artfynd.xlsx
+++ b/artfynd/A 55334-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128692035</v>
       </c>
       <c r="B2" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128691766</v>
       </c>
       <c r="B3" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>128691679</v>
       </c>
       <c r="B4" t="n">
-        <v>90261</v>
+        <v>90266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 55334-2024 artfynd.xlsx
+++ b/artfynd/A 55334-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128692035</v>
       </c>
       <c r="B2" t="n">
-        <v>92434</v>
+        <v>92439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128691766</v>
       </c>
       <c r="B3" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>128691679</v>
       </c>
       <c r="B4" t="n">
-        <v>90266</v>
+        <v>90271</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 55334-2024 artfynd.xlsx
+++ b/artfynd/A 55334-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128692035</v>
       </c>
       <c r="B2" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128691766</v>
       </c>
       <c r="B3" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>128691679</v>
       </c>
       <c r="B4" t="n">
-        <v>90271</v>
+        <v>90275</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 55334-2024 artfynd.xlsx
+++ b/artfynd/A 55334-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128692035</v>
       </c>
       <c r="B2" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128691766</v>
       </c>
       <c r="B3" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>128691679</v>
       </c>
       <c r="B4" t="n">
-        <v>90275</v>
+        <v>90280</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 55334-2024 artfynd.xlsx
+++ b/artfynd/A 55334-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128692035</v>
       </c>
       <c r="B2" t="n">
-        <v>92456</v>
+        <v>92461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128691766</v>
       </c>
       <c r="B3" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>128691679</v>
       </c>
       <c r="B4" t="n">
-        <v>90287</v>
+        <v>90290</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 55334-2024 artfynd.xlsx
+++ b/artfynd/A 55334-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128692035</v>
       </c>
       <c r="B2" t="n">
-        <v>92461</v>
+        <v>92464</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128691766</v>
       </c>
       <c r="B3" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>128691679</v>
       </c>
       <c r="B4" t="n">
-        <v>90290</v>
+        <v>90293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 55334-2024 artfynd.xlsx
+++ b/artfynd/A 55334-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128692035</v>
       </c>
       <c r="B2" t="n">
-        <v>92464</v>
+        <v>92471</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128691766</v>
       </c>
       <c r="B3" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>128691679</v>
       </c>
       <c r="B4" t="n">
-        <v>90293</v>
+        <v>90297</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
